--- a/test-case-exports/Registration.xlsx
+++ b/test-case-exports/Registration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4363" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4371" uniqueCount="612">
   <si>
     <t>#</t>
   </si>
@@ -909,6 +909,15 @@
     <t>should enable the Verify button once the 20-second countdown expires [EMI-4937]</t>
   </si>
   <si>
+    <t>BusinessTestCases/Registration/functional/RegistrationOtpAdminConfig.spec.ts</t>
+  </si>
+  <si>
+    <t>Registration — Admin OTP Configuration</t>
+  </si>
+  <si>
+    <t>registration OTP operation is locked on (checked and not editable) in the default OTP setting</t>
+  </si>
+  <si>
     <t>BusinessTestCases/Registration/functional/RegistrationOtpFunctionality.spec.ts</t>
   </si>
   <si>
@@ -1827,7 +1836,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-09-08T15:08:53.641Z</t>
+    <t>2026-09-09T06:44:10.199Z</t>
   </si>
   <si>
     <t>Total test cases</t>
@@ -2256,7 +2265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I542"/>
+  <dimension ref="A1:I543"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -8861,16 +8870,16 @@
         <v>9</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>14</v>
@@ -8890,16 +8899,16 @@
         <v>9</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>14</v>
@@ -8919,16 +8928,16 @@
         <v>9</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>14</v>
@@ -8948,16 +8957,16 @@
         <v>9</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>14</v>
@@ -8977,16 +8986,16 @@
         <v>9</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>14</v>
@@ -9006,16 +9015,16 @@
         <v>9</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>14</v>
@@ -9035,16 +9044,16 @@
         <v>9</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>14</v>
@@ -9064,16 +9073,16 @@
         <v>9</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>14</v>
@@ -9093,16 +9102,16 @@
         <v>9</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>14</v>
@@ -9122,16 +9131,16 @@
         <v>9</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>14</v>
@@ -9151,16 +9160,16 @@
         <v>9</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>14</v>
@@ -9180,10 +9189,10 @@
         <v>9</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>12</v>
@@ -9192,13 +9201,13 @@
         <v>311</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I239" s="2" t="s">
-        <v>312</v>
+        <v>12</v>
       </c>
     </row>
     <row r="240" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9209,25 +9218,25 @@
         <v>9</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I240" s="2" t="s">
-        <v>12</v>
+        <v>315</v>
       </c>
     </row>
     <row r="241" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9238,16 +9247,16 @@
         <v>9</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>14</v>
@@ -9267,25 +9276,25 @@
         <v>9</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="I242" s="2" t="s">
-        <v>317</v>
+        <v>12</v>
       </c>
     </row>
     <row r="243" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9296,25 +9305,25 @@
         <v>9</v>
       </c>
       <c r="C243" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D243" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D243" s="2" t="s">
+      <c r="E243" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F243" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E243" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F243" s="2" t="s">
+      <c r="G243" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H243" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I243" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="G243" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H243" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I243" s="2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="244" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9325,16 +9334,16 @@
         <v>9</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>154</v>
@@ -9343,7 +9352,7 @@
         <v>15</v>
       </c>
       <c r="I244" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="245" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9354,25 +9363,25 @@
         <v>9</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I245" s="2" t="s">
-        <v>12</v>
+        <v>326</v>
       </c>
     </row>
     <row r="246" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9383,16 +9392,16 @@
         <v>9</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>14</v>
@@ -9412,16 +9421,16 @@
         <v>9</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>14</v>
@@ -9441,16 +9450,16 @@
         <v>9</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>14</v>
@@ -9470,16 +9479,16 @@
         <v>9</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>14</v>
@@ -9499,16 +9508,16 @@
         <v>9</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>14</v>
@@ -9528,16 +9537,16 @@
         <v>9</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>14</v>
@@ -9557,16 +9566,16 @@
         <v>9</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>14</v>
@@ -9586,16 +9595,16 @@
         <v>9</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>14</v>
@@ -9615,16 +9624,16 @@
         <v>9</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>14</v>
@@ -9644,16 +9653,16 @@
         <v>9</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>14</v>
@@ -9673,16 +9682,16 @@
         <v>9</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>14</v>
@@ -9702,16 +9711,16 @@
         <v>9</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>14</v>
@@ -9731,16 +9740,16 @@
         <v>9</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>14</v>
@@ -9760,16 +9769,16 @@
         <v>9</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>14</v>
@@ -9789,16 +9798,16 @@
         <v>9</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>14</v>
@@ -9818,16 +9827,16 @@
         <v>9</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>14</v>
@@ -9847,16 +9856,16 @@
         <v>9</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>14</v>
@@ -9876,25 +9885,25 @@
         <v>9</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="I263" s="2" t="s">
-        <v>345</v>
+        <v>12</v>
       </c>
     </row>
     <row r="264" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9905,25 +9914,25 @@
         <v>9</v>
       </c>
       <c r="C264" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D264" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="D264" s="2" t="s">
+      <c r="E264" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F264" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="E264" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F264" s="2" t="s">
+      <c r="G264" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H264" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I264" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="G264" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H264" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I264" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="265" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9934,16 +9943,16 @@
         <v>9</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>14</v>
@@ -9963,7 +9972,7 @@
         <v>9</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>350</v>
@@ -9972,13 +9981,13 @@
         <v>12</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="I266" s="2" t="s">
         <v>12</v>
@@ -9992,16 +10001,16 @@
         <v>9</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>14</v>
@@ -10010,7 +10019,7 @@
         <v>46</v>
       </c>
       <c r="I267" s="2" t="s">
-        <v>354</v>
+        <v>12</v>
       </c>
     </row>
     <row r="268" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10021,16 +10030,16 @@
         <v>9</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>14</v>
@@ -10039,7 +10048,7 @@
         <v>46</v>
       </c>
       <c r="I268" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="269" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10050,16 +10059,16 @@
         <v>9</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>14</v>
@@ -10068,7 +10077,7 @@
         <v>46</v>
       </c>
       <c r="I269" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="270" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10079,25 +10088,25 @@
         <v>9</v>
       </c>
       <c r="C270" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F270" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G270" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H270" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I270" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="E270" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F270" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G270" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H270" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I270" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="271" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10108,16 +10117,16 @@
         <v>9</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>14</v>
@@ -10137,16 +10146,16 @@
         <v>9</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>14</v>
@@ -10166,16 +10175,16 @@
         <v>9</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>359</v>
+        <v>115</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>14</v>
@@ -10195,16 +10204,16 @@
         <v>9</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>14</v>
@@ -10224,16 +10233,16 @@
         <v>9</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>14</v>
@@ -10253,16 +10262,16 @@
         <v>9</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
@@ -10282,16 +10291,16 @@
         <v>9</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
@@ -10311,16 +10320,16 @@
         <v>9</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>14</v>
@@ -10340,16 +10349,16 @@
         <v>9</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>14</v>
@@ -10369,16 +10378,16 @@
         <v>9</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>14</v>
@@ -10398,16 +10407,16 @@
         <v>9</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>14</v>
@@ -10427,16 +10436,16 @@
         <v>9</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>14</v>
@@ -10456,16 +10465,16 @@
         <v>9</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>108</v>
+        <v>371</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
@@ -10485,16 +10494,16 @@
         <v>9</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>369</v>
+        <v>108</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>14</v>
@@ -10514,16 +10523,16 @@
         <v>9</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>14</v>
@@ -10543,16 +10552,16 @@
         <v>9</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>14</v>
@@ -10572,16 +10581,16 @@
         <v>9</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>14</v>
@@ -10601,16 +10610,16 @@
         <v>9</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>14</v>
@@ -10630,16 +10639,16 @@
         <v>9</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>14</v>
@@ -10659,16 +10668,16 @@
         <v>9</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>14</v>
@@ -10688,16 +10697,16 @@
         <v>9</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>14</v>
@@ -10717,16 +10726,16 @@
         <v>9</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>14</v>
@@ -10746,16 +10755,16 @@
         <v>9</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>14</v>
@@ -10775,16 +10784,16 @@
         <v>9</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>14</v>
@@ -10804,16 +10813,16 @@
         <v>9</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>14</v>
@@ -10833,16 +10842,16 @@
         <v>9</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>14</v>
@@ -10862,16 +10871,16 @@
         <v>9</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>14</v>
@@ -10891,22 +10900,22 @@
         <v>9</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="I298" s="2" t="s">
         <v>12</v>
@@ -10920,16 +10929,16 @@
         <v>9</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>14</v>
@@ -10949,16 +10958,16 @@
         <v>9</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>14</v>
@@ -10978,16 +10987,16 @@
         <v>9</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>14</v>
@@ -11007,16 +11016,16 @@
         <v>9</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>14</v>
@@ -11036,16 +11045,16 @@
         <v>9</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>388</v>
+        <v>12</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>14</v>
@@ -11065,16 +11074,16 @@
         <v>9</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>14</v>
@@ -11094,16 +11103,16 @@
         <v>9</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>14</v>
@@ -11123,16 +11132,16 @@
         <v>9</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>14</v>
@@ -11152,16 +11161,16 @@
         <v>9</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>14</v>
@@ -11181,16 +11190,16 @@
         <v>9</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>14</v>
@@ -11210,16 +11219,16 @@
         <v>9</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>14</v>
@@ -11239,16 +11248,16 @@
         <v>9</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>14</v>
@@ -11268,16 +11277,16 @@
         <v>9</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>14</v>
@@ -11297,16 +11306,16 @@
         <v>9</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>14</v>
@@ -11326,22 +11335,22 @@
         <v>9</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>399</v>
+        <v>360</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>400</v>
+        <v>361</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>12</v>
+        <v>391</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>94</v>
+        <v>401</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="I313" s="2" t="s">
         <v>12</v>
@@ -11355,16 +11364,16 @@
         <v>9</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>14</v>
@@ -11384,16 +11393,16 @@
         <v>9</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>14</v>
@@ -11413,16 +11422,16 @@
         <v>9</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>14</v>
@@ -11442,16 +11451,16 @@
         <v>9</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>14</v>
@@ -11471,16 +11480,16 @@
         <v>9</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>401</v>
+        <v>98</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>14</v>
@@ -11500,16 +11509,16 @@
         <v>9</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>14</v>
@@ -11529,16 +11538,16 @@
         <v>9</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>14</v>
@@ -11558,16 +11567,16 @@
         <v>9</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>102</v>
+        <v>406</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>14</v>
@@ -11587,16 +11596,16 @@
         <v>9</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>404</v>
+        <v>102</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>14</v>
@@ -11616,16 +11625,16 @@
         <v>9</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>14</v>
@@ -11645,16 +11654,16 @@
         <v>9</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>14</v>
@@ -11674,16 +11683,16 @@
         <v>9</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>14</v>
@@ -11703,16 +11712,16 @@
         <v>9</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>14</v>
@@ -11732,16 +11741,16 @@
         <v>9</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E327" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>14</v>
@@ -11761,16 +11770,16 @@
         <v>9</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>14</v>
@@ -11790,16 +11799,16 @@
         <v>9</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>14</v>
@@ -11819,16 +11828,16 @@
         <v>9</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>14</v>
@@ -11848,16 +11857,16 @@
         <v>9</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>14</v>
@@ -11877,16 +11886,16 @@
         <v>9</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>14</v>
@@ -11906,16 +11915,16 @@
         <v>9</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E333" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>94</v>
+        <v>417</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>14</v>
@@ -11935,16 +11944,16 @@
         <v>9</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>417</v>
+        <v>94</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>14</v>
@@ -11964,16 +11973,16 @@
         <v>9</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>96</v>
+        <v>420</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>14</v>
@@ -11993,16 +12002,16 @@
         <v>9</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>418</v>
+        <v>96</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>14</v>
@@ -12022,16 +12031,16 @@
         <v>9</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>98</v>
+        <v>421</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>14</v>
@@ -12051,16 +12060,16 @@
         <v>9</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E338" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>419</v>
+        <v>98</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>14</v>
@@ -12080,16 +12089,16 @@
         <v>9</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>14</v>
@@ -12109,16 +12118,16 @@
         <v>9</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>14</v>
@@ -12138,16 +12147,16 @@
         <v>9</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>14</v>
@@ -12167,16 +12176,16 @@
         <v>9</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>14</v>
@@ -12196,16 +12205,16 @@
         <v>9</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>14</v>
@@ -12225,16 +12234,16 @@
         <v>9</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>14</v>
@@ -12254,16 +12263,16 @@
         <v>9</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>14</v>
@@ -12283,16 +12292,16 @@
         <v>9</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>14</v>
@@ -12312,16 +12321,16 @@
         <v>9</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>14</v>
@@ -12341,16 +12350,16 @@
         <v>9</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>14</v>
@@ -12370,16 +12379,16 @@
         <v>9</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>14</v>
@@ -12399,16 +12408,16 @@
         <v>9</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>14</v>
@@ -12428,16 +12437,16 @@
         <v>9</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>14</v>
@@ -12457,16 +12466,16 @@
         <v>9</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>14</v>
@@ -12486,16 +12495,16 @@
         <v>9</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>14</v>
@@ -12515,16 +12524,16 @@
         <v>9</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>14</v>
@@ -12544,16 +12553,16 @@
         <v>9</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>14</v>
@@ -12573,16 +12582,16 @@
         <v>9</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>14</v>
@@ -12602,16 +12611,16 @@
         <v>9</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>14</v>
@@ -12631,16 +12640,16 @@
         <v>9</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F358" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>14</v>
@@ -12660,16 +12669,16 @@
         <v>9</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E359" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>14</v>
@@ -12689,16 +12698,16 @@
         <v>9</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E360" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>113</v>
+        <v>443</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>14</v>
@@ -12718,16 +12727,16 @@
         <v>9</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E361" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>441</v>
+        <v>113</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>14</v>
@@ -12747,16 +12756,16 @@
         <v>9</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>14</v>
@@ -12776,16 +12785,16 @@
         <v>9</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E363" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>14</v>
@@ -12805,16 +12814,16 @@
         <v>9</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>443</v>
+        <v>388</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>14</v>
@@ -12834,16 +12843,16 @@
         <v>9</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E365" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>14</v>
@@ -12863,16 +12872,16 @@
         <v>9</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>386</v>
+        <v>447</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>14</v>
@@ -12892,16 +12901,16 @@
         <v>9</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E367" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>14</v>
@@ -12921,16 +12930,16 @@
         <v>9</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="E368" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>138</v>
+        <v>390</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>14</v>
@@ -12950,16 +12959,16 @@
         <v>9</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E369" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>14</v>
@@ -12979,16 +12988,16 @@
         <v>9</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E370" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>14</v>
@@ -13008,16 +13017,16 @@
         <v>9</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E371" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>446</v>
+        <v>140</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>14</v>
@@ -13037,16 +13046,16 @@
         <v>9</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E372" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>158</v>
+        <v>449</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>14</v>
@@ -13066,16 +13075,16 @@
         <v>9</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E373" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>14</v>
@@ -13095,16 +13104,16 @@
         <v>9</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E374" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>447</v>
+        <v>160</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>14</v>
@@ -13124,16 +13133,16 @@
         <v>9</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E375" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>14</v>
@@ -13153,16 +13162,16 @@
         <v>9</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E376" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>14</v>
@@ -13182,16 +13191,16 @@
         <v>9</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E377" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>137</v>
+        <v>452</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>14</v>
@@ -13211,16 +13220,16 @@
         <v>9</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>451</v>
+        <v>418</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>453</v>
+        <v>12</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>454</v>
+        <v>137</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>14</v>
@@ -13240,16 +13249,16 @@
         <v>9</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>14</v>
@@ -13269,16 +13278,16 @@
         <v>9</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>14</v>
@@ -13298,16 +13307,16 @@
         <v>9</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>14</v>
@@ -13327,16 +13336,16 @@
         <v>9</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>14</v>
@@ -13356,16 +13365,16 @@
         <v>9</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>14</v>
@@ -13385,16 +13394,16 @@
         <v>9</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>14</v>
@@ -13414,16 +13423,16 @@
         <v>9</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>14</v>
@@ -13443,16 +13452,16 @@
         <v>9</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>14</v>
@@ -13472,16 +13481,16 @@
         <v>9</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>14</v>
@@ -13501,16 +13510,16 @@
         <v>9</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>14</v>
@@ -13530,16 +13539,16 @@
         <v>9</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>14</v>
@@ -13559,16 +13568,16 @@
         <v>9</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>14</v>
@@ -13588,16 +13597,16 @@
         <v>9</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>14</v>
@@ -13617,16 +13626,16 @@
         <v>9</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>14</v>
@@ -13646,16 +13655,16 @@
         <v>9</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>14</v>
@@ -13675,16 +13684,16 @@
         <v>9</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>14</v>
@@ -13704,16 +13713,16 @@
         <v>9</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>14</v>
@@ -13733,16 +13742,16 @@
         <v>9</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F396" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>14</v>
@@ -13762,16 +13771,16 @@
         <v>9</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>14</v>
@@ -13791,16 +13800,16 @@
         <v>9</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>14</v>
@@ -13820,16 +13829,16 @@
         <v>9</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>14</v>
@@ -13849,16 +13858,16 @@
         <v>9</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>14</v>
@@ -13878,16 +13887,16 @@
         <v>9</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>14</v>
@@ -13907,16 +13916,16 @@
         <v>9</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>14</v>
@@ -13936,16 +13945,16 @@
         <v>9</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>14</v>
@@ -13965,16 +13974,16 @@
         <v>9</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F404" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>14</v>
@@ -13994,16 +14003,16 @@
         <v>9</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F405" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>14</v>
@@ -14023,16 +14032,16 @@
         <v>9</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F406" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>14</v>
@@ -14052,16 +14061,16 @@
         <v>9</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F407" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>14</v>
@@ -14081,16 +14090,16 @@
         <v>9</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F408" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>14</v>
@@ -14110,16 +14119,16 @@
         <v>9</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F409" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>14</v>
@@ -14139,16 +14148,16 @@
         <v>9</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F410" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>14</v>
@@ -14168,16 +14177,16 @@
         <v>9</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F411" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>14</v>
@@ -14197,16 +14206,16 @@
         <v>9</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F412" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>14</v>
@@ -14226,16 +14235,16 @@
         <v>9</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F413" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>14</v>
@@ -14255,16 +14264,16 @@
         <v>9</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F414" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>14</v>
@@ -14284,16 +14293,16 @@
         <v>9</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F415" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>14</v>
@@ -14313,16 +14322,16 @@
         <v>9</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F416" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>14</v>
@@ -14342,16 +14351,16 @@
         <v>9</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F417" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>14</v>
@@ -14371,16 +14380,16 @@
         <v>9</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F418" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>14</v>
@@ -14400,16 +14409,16 @@
         <v>9</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F419" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>14</v>
@@ -14429,16 +14438,16 @@
         <v>9</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F420" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>14</v>
@@ -14458,22 +14467,22 @@
         <v>9</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="F421" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H421" s="2" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="I421" s="2" t="s">
         <v>12</v>
@@ -14487,16 +14496,16 @@
         <v>9</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F422" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>14</v>
@@ -14516,16 +14525,16 @@
         <v>9</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F423" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>14</v>
@@ -14545,16 +14554,16 @@
         <v>9</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F424" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>14</v>
@@ -14574,16 +14583,16 @@
         <v>9</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F425" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>14</v>
@@ -14603,16 +14612,16 @@
         <v>9</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F426" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>14</v>
@@ -14632,16 +14641,16 @@
         <v>9</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F427" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>14</v>
@@ -14661,16 +14670,16 @@
         <v>9</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F428" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>14</v>
@@ -14690,13 +14699,13 @@
         <v>9</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>509</v>
+        <v>454</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>510</v>
+        <v>455</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>12</v>
+        <v>503</v>
       </c>
       <c r="F429" s="2" t="s">
         <v>511</v>
@@ -14705,7 +14714,7 @@
         <v>14</v>
       </c>
       <c r="H429" s="2" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="I429" s="2" t="s">
         <v>12</v>
@@ -14719,16 +14728,16 @@
         <v>9</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E430" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F430" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>14</v>
@@ -14748,16 +14757,16 @@
         <v>9</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E431" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F431" s="2" t="s">
-        <v>94</v>
+        <v>515</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>14</v>
@@ -14777,16 +14786,16 @@
         <v>9</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E432" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F432" s="2" t="s">
-        <v>513</v>
+        <v>94</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>14</v>
@@ -14806,16 +14815,16 @@
         <v>9</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E433" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F433" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>14</v>
@@ -14835,16 +14844,16 @@
         <v>9</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E434" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F434" s="2" t="s">
-        <v>96</v>
+        <v>517</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>14</v>
@@ -14864,16 +14873,16 @@
         <v>9</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E435" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>515</v>
+        <v>96</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>14</v>
@@ -14893,16 +14902,16 @@
         <v>9</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F436" s="2" t="s">
-        <v>418</v>
+        <v>518</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>14</v>
@@ -14922,16 +14931,16 @@
         <v>9</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F437" s="2" t="s">
-        <v>516</v>
+        <v>421</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>14</v>
@@ -14951,16 +14960,16 @@
         <v>9</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E438" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F438" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>14</v>
@@ -14980,16 +14989,16 @@
         <v>9</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F439" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>14</v>
@@ -15009,16 +15018,16 @@
         <v>9</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F440" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>14</v>
@@ -15038,16 +15047,16 @@
         <v>9</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E441" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F441" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>14</v>
@@ -15067,16 +15076,16 @@
         <v>9</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E442" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F442" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>14</v>
@@ -15096,16 +15105,16 @@
         <v>9</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F443" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>14</v>
@@ -15125,16 +15134,16 @@
         <v>9</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F444" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>14</v>
@@ -15154,16 +15163,16 @@
         <v>9</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E445" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F445" s="2" t="s">
-        <v>441</v>
+        <v>526</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>14</v>
@@ -15183,16 +15192,16 @@
         <v>9</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E446" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F446" s="2" t="s">
-        <v>524</v>
+        <v>444</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>14</v>
@@ -15212,16 +15221,16 @@
         <v>9</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E447" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F447" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>14</v>
@@ -15241,16 +15250,16 @@
         <v>9</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F448" s="2" t="s">
-        <v>443</v>
+        <v>528</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>14</v>
@@ -15270,16 +15279,16 @@
         <v>9</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F449" s="2" t="s">
-        <v>94</v>
+        <v>446</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>14</v>
@@ -15299,16 +15308,16 @@
         <v>9</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F450" s="2" t="s">
-        <v>417</v>
+        <v>94</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>14</v>
@@ -15328,16 +15337,16 @@
         <v>9</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E451" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F451" s="2" t="s">
-        <v>96</v>
+        <v>420</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>14</v>
@@ -15357,16 +15366,16 @@
         <v>9</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F452" s="2" t="s">
-        <v>418</v>
+        <v>96</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>14</v>
@@ -15386,16 +15395,16 @@
         <v>9</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E453" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F453" s="2" t="s">
-        <v>517</v>
+        <v>421</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>14</v>
@@ -15415,16 +15424,16 @@
         <v>9</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E454" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>14</v>
@@ -15444,16 +15453,16 @@
         <v>9</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E455" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F455" s="2" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>14</v>
@@ -15473,16 +15482,16 @@
         <v>9</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E456" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F456" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>14</v>
@@ -15502,16 +15511,16 @@
         <v>9</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E457" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F457" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>14</v>
@@ -15531,16 +15540,16 @@
         <v>9</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E458" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F458" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>14</v>
@@ -15560,16 +15569,16 @@
         <v>9</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E459" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F459" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>14</v>
@@ -15589,16 +15598,16 @@
         <v>9</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E460" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F460" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>14</v>
@@ -15618,16 +15627,16 @@
         <v>9</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E461" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F461" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>14</v>
@@ -15647,16 +15656,16 @@
         <v>9</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E462" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F462" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>14</v>
@@ -15676,16 +15685,16 @@
         <v>9</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E463" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F463" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>14</v>
@@ -15705,16 +15714,16 @@
         <v>9</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E464" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F464" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>14</v>
@@ -15734,16 +15743,16 @@
         <v>9</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E465" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F465" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>14</v>
@@ -15763,16 +15772,16 @@
         <v>9</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E466" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F466" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>14</v>
@@ -15792,10 +15801,10 @@
         <v>9</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="E467" s="2" t="s">
         <v>12</v>
@@ -15821,16 +15830,16 @@
         <v>9</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E468" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F468" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>14</v>
@@ -15850,16 +15859,16 @@
         <v>9</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E469" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F469" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>14</v>
@@ -15879,16 +15888,16 @@
         <v>9</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E470" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F470" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>14</v>
@@ -15908,16 +15917,16 @@
         <v>9</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E471" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F471" s="2" t="s">
-        <v>413</v>
+        <v>548</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>14</v>
@@ -15937,16 +15946,16 @@
         <v>9</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E472" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F472" s="2" t="s">
-        <v>546</v>
+        <v>416</v>
       </c>
       <c r="G472" s="2" t="s">
         <v>14</v>
@@ -15966,16 +15975,16 @@
         <v>9</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E473" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F473" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="G473" s="2" t="s">
         <v>14</v>
@@ -15995,16 +16004,16 @@
         <v>9</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="E474" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F474" s="2" t="s">
-        <v>94</v>
+        <v>550</v>
       </c>
       <c r="G474" s="2" t="s">
         <v>14</v>
@@ -16024,16 +16033,16 @@
         <v>9</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E475" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F475" s="2" t="s">
-        <v>417</v>
+        <v>94</v>
       </c>
       <c r="G475" s="2" t="s">
         <v>14</v>
@@ -16053,16 +16062,16 @@
         <v>9</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D476" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E476" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F476" s="2" t="s">
-        <v>96</v>
+        <v>420</v>
       </c>
       <c r="G476" s="2" t="s">
         <v>14</v>
@@ -16082,16 +16091,16 @@
         <v>9</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E477" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F477" s="2" t="s">
-        <v>418</v>
+        <v>96</v>
       </c>
       <c r="G477" s="2" t="s">
         <v>14</v>
@@ -16111,16 +16120,16 @@
         <v>9</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E478" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F478" s="2" t="s">
-        <v>517</v>
+        <v>421</v>
       </c>
       <c r="G478" s="2" t="s">
         <v>14</v>
@@ -16140,16 +16149,16 @@
         <v>9</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E479" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F479" s="2" t="s">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="G479" s="2" t="s">
         <v>14</v>
@@ -16169,16 +16178,16 @@
         <v>9</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E480" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F480" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="G480" s="2" t="s">
         <v>14</v>
@@ -16198,16 +16207,16 @@
         <v>9</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E481" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F481" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G481" s="2" t="s">
         <v>14</v>
@@ -16227,16 +16236,16 @@
         <v>9</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E482" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F482" s="2" t="s">
-        <v>102</v>
+        <v>555</v>
       </c>
       <c r="G482" s="2" t="s">
         <v>14</v>
@@ -16256,16 +16265,16 @@
         <v>9</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E483" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F483" s="2" t="s">
-        <v>553</v>
+        <v>102</v>
       </c>
       <c r="G483" s="2" t="s">
         <v>14</v>
@@ -16285,16 +16294,16 @@
         <v>9</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E484" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F484" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G484" s="2" t="s">
         <v>14</v>
@@ -16314,16 +16323,16 @@
         <v>9</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E485" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F485" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="G485" s="2" t="s">
         <v>14</v>
@@ -16343,16 +16352,16 @@
         <v>9</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E486" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F486" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G486" s="2" t="s">
         <v>14</v>
@@ -16372,16 +16381,16 @@
         <v>9</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E487" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F487" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="G487" s="2" t="s">
         <v>14</v>
@@ -16401,16 +16410,16 @@
         <v>9</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E488" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F488" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G488" s="2" t="s">
         <v>14</v>
@@ -16430,16 +16439,16 @@
         <v>9</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E489" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F489" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G489" s="2" t="s">
         <v>14</v>
@@ -16459,16 +16468,16 @@
         <v>9</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E490" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F490" s="2" t="s">
-        <v>413</v>
+        <v>562</v>
       </c>
       <c r="G490" s="2" t="s">
         <v>14</v>
@@ -16488,16 +16497,16 @@
         <v>9</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E491" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F491" s="2" t="s">
-        <v>560</v>
+        <v>416</v>
       </c>
       <c r="G491" s="2" t="s">
         <v>14</v>
@@ -16517,16 +16526,16 @@
         <v>9</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E492" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F492" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G492" s="2" t="s">
         <v>14</v>
@@ -16546,10 +16555,10 @@
         <v>9</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="E493" s="2" t="s">
         <v>12</v>
@@ -16575,16 +16584,16 @@
         <v>9</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E494" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F494" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="G494" s="2" t="s">
         <v>14</v>
@@ -16604,16 +16613,16 @@
         <v>9</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E495" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F495" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G495" s="2" t="s">
         <v>14</v>
@@ -16633,16 +16642,16 @@
         <v>9</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E496" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F496" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="G496" s="2" t="s">
         <v>14</v>
@@ -16662,16 +16671,16 @@
         <v>9</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E497" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F497" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G497" s="2" t="s">
         <v>14</v>
@@ -16691,16 +16700,16 @@
         <v>9</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F498" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="G498" s="2" t="s">
         <v>14</v>
@@ -16720,16 +16729,16 @@
         <v>9</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F499" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="G499" s="2" t="s">
         <v>14</v>
@@ -16749,16 +16758,16 @@
         <v>9</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E500" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F500" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="G500" s="2" t="s">
         <v>14</v>
@@ -16778,16 +16787,16 @@
         <v>9</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E501" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F501" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G501" s="2" t="s">
         <v>14</v>
@@ -16807,16 +16816,16 @@
         <v>9</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D502" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E502" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F502" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G502" s="2" t="s">
         <v>14</v>
@@ -16836,16 +16845,16 @@
         <v>9</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D503" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E503" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F503" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G503" s="2" t="s">
         <v>14</v>
@@ -16865,16 +16874,16 @@
         <v>9</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E504" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F504" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="G504" s="2" t="s">
         <v>14</v>
@@ -16894,16 +16903,16 @@
         <v>9</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D505" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E505" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F505" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="G505" s="2" t="s">
         <v>14</v>
@@ -16923,16 +16932,16 @@
         <v>9</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E506" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F506" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G506" s="2" t="s">
         <v>14</v>
@@ -16952,16 +16961,16 @@
         <v>9</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E507" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F507" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G507" s="2" t="s">
         <v>14</v>
@@ -16981,16 +16990,16 @@
         <v>9</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E508" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F508" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G508" s="2" t="s">
         <v>14</v>
@@ -17010,16 +17019,16 @@
         <v>9</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D509" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E509" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F509" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="G509" s="2" t="s">
         <v>14</v>
@@ -17039,16 +17048,16 @@
         <v>9</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D510" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E510" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F510" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="G510" s="2" t="s">
         <v>14</v>
@@ -17068,16 +17077,16 @@
         <v>9</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E511" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F511" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G511" s="2" t="s">
         <v>14</v>
@@ -17097,16 +17106,16 @@
         <v>9</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E512" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F512" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G512" s="2" t="s">
         <v>14</v>
@@ -17126,16 +17135,16 @@
         <v>9</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>585</v>
+        <v>566</v>
       </c>
       <c r="E513" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F513" s="2" t="s">
-        <v>94</v>
+        <v>586</v>
       </c>
       <c r="G513" s="2" t="s">
         <v>14</v>
@@ -17155,16 +17164,16 @@
         <v>9</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E514" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F514" s="2" t="s">
-        <v>417</v>
+        <v>94</v>
       </c>
       <c r="G514" s="2" t="s">
         <v>14</v>
@@ -17184,16 +17193,16 @@
         <v>9</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E515" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F515" s="2" t="s">
-        <v>96</v>
+        <v>420</v>
       </c>
       <c r="G515" s="2" t="s">
         <v>14</v>
@@ -17213,16 +17222,16 @@
         <v>9</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E516" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F516" s="2" t="s">
-        <v>418</v>
+        <v>96</v>
       </c>
       <c r="G516" s="2" t="s">
         <v>14</v>
@@ -17242,16 +17251,16 @@
         <v>9</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D517" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E517" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F517" s="2" t="s">
-        <v>98</v>
+        <v>421</v>
       </c>
       <c r="G517" s="2" t="s">
         <v>14</v>
@@ -17271,16 +17280,16 @@
         <v>9</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D518" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E518" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F518" s="2" t="s">
-        <v>586</v>
+        <v>98</v>
       </c>
       <c r="G518" s="2" t="s">
         <v>14</v>
@@ -17300,16 +17309,16 @@
         <v>9</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D519" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E519" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F519" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="G519" s="2" t="s">
         <v>14</v>
@@ -17329,16 +17338,16 @@
         <v>9</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D520" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E520" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F520" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G520" s="2" t="s">
         <v>14</v>
@@ -17358,16 +17367,16 @@
         <v>9</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D521" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E521" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F521" s="2" t="s">
-        <v>359</v>
+        <v>591</v>
       </c>
       <c r="G521" s="2" t="s">
         <v>14</v>
@@ -17387,16 +17396,16 @@
         <v>9</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D522" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E522" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F522" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G522" s="2" t="s">
         <v>14</v>
@@ -17416,16 +17425,16 @@
         <v>9</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D523" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E523" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F523" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G523" s="2" t="s">
         <v>14</v>
@@ -17445,16 +17454,16 @@
         <v>9</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D524" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E524" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F524" s="2" t="s">
-        <v>589</v>
+        <v>364</v>
       </c>
       <c r="G524" s="2" t="s">
         <v>14</v>
@@ -17474,16 +17483,16 @@
         <v>9</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D525" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E525" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F525" s="2" t="s">
-        <v>369</v>
+        <v>592</v>
       </c>
       <c r="G525" s="2" t="s">
         <v>14</v>
@@ -17503,16 +17512,16 @@
         <v>9</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D526" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E526" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F526" s="2" t="s">
-        <v>590</v>
+        <v>372</v>
       </c>
       <c r="G526" s="2" t="s">
         <v>14</v>
@@ -17532,16 +17541,16 @@
         <v>9</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D527" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E527" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F527" s="2" t="s">
-        <v>368</v>
+        <v>593</v>
       </c>
       <c r="G527" s="2" t="s">
         <v>14</v>
@@ -17561,16 +17570,16 @@
         <v>9</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D528" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E528" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F528" s="2" t="s">
-        <v>108</v>
+        <v>371</v>
       </c>
       <c r="G528" s="2" t="s">
         <v>14</v>
@@ -17590,16 +17599,16 @@
         <v>9</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E529" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F529" s="2" t="s">
-        <v>370</v>
+        <v>108</v>
       </c>
       <c r="G529" s="2" t="s">
         <v>14</v>
@@ -17619,16 +17628,16 @@
         <v>9</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D530" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E530" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F530" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G530" s="2" t="s">
         <v>14</v>
@@ -17648,16 +17657,16 @@
         <v>9</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D531" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E531" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F531" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G531" s="2" t="s">
         <v>14</v>
@@ -17677,16 +17686,16 @@
         <v>9</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D532" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E532" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F532" s="2" t="s">
-        <v>591</v>
+        <v>375</v>
       </c>
       <c r="G532" s="2" t="s">
         <v>14</v>
@@ -17706,16 +17715,16 @@
         <v>9</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D533" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E533" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F533" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G533" s="2" t="s">
         <v>14</v>
@@ -17735,16 +17744,16 @@
         <v>9</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E534" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F534" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="G534" s="2" t="s">
         <v>14</v>
@@ -17764,16 +17773,16 @@
         <v>9</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E535" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F535" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G535" s="2" t="s">
         <v>14</v>
@@ -17793,16 +17802,16 @@
         <v>9</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D536" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E536" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F536" s="2" t="s">
-        <v>113</v>
+        <v>597</v>
       </c>
       <c r="G536" s="2" t="s">
         <v>14</v>
@@ -17822,16 +17831,16 @@
         <v>9</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E537" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F537" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G537" s="2" t="s">
         <v>14</v>
@@ -17851,16 +17860,16 @@
         <v>9</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D538" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E538" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F538" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G538" s="2" t="s">
         <v>14</v>
@@ -17880,16 +17889,16 @@
         <v>9</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E539" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F539" s="2" t="s">
-        <v>385</v>
+        <v>115</v>
       </c>
       <c r="G539" s="2" t="s">
         <v>14</v>
@@ -17909,16 +17918,16 @@
         <v>9</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E540" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F540" s="2" t="s">
-        <v>443</v>
+        <v>388</v>
       </c>
       <c r="G540" s="2" t="s">
         <v>14</v>
@@ -17938,16 +17947,16 @@
         <v>9</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E541" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F541" s="2" t="s">
-        <v>595</v>
+        <v>446</v>
       </c>
       <c r="G541" s="2" t="s">
         <v>14</v>
@@ -17967,16 +17976,16 @@
         <v>9</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E542" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F542" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G542" s="2" t="s">
         <v>14</v>
@@ -17988,8 +17997,37 @@
         <v>12</v>
       </c>
     </row>
+    <row r="543" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A543" s="2">
+        <v>542</v>
+      </c>
+      <c r="B543" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C543" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D543" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E543" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F543" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="G543" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H543" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I543" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I542"/>
+  <autoFilter ref="A1:I543"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -18006,7 +18044,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>12</v>
@@ -18022,18 +18060,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B3" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B4">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -18046,7 +18084,7 @@
     </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>12</v>
@@ -18054,7 +18092,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="B7">
         <v>45</v>
@@ -18062,7 +18100,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B8">
         <v>34</v>
@@ -18070,15 +18108,15 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B9">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B10">
         <v>230</v>
@@ -18094,7 +18132,7 @@
     </row>
     <row r="12" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>12</v>
@@ -18105,7 +18143,7 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -18134,7 +18172,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -18142,10 +18180,10 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B18">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
